--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table62.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table62.xlsx
@@ -586,7 +586,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -779,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -795,7 +795,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -805,36 +826,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1323,19 +1331,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1"/>
@@ -1351,7 +1359,7 @@
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1375,10 +1383,10 @@
       <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="15" t="s">
@@ -1386,7 +1394,7 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1410,24 +1418,24 @@
       <c r="H4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="18"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="16"/>
     </row>
     <row r="5" spans="1:11" ht="17.5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
@@ -2445,54 +2453,54 @@
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="10">
         <v>29444</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="10">
         <v>30244</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="10">
         <v>28552</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="10">
         <v>30840</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="10">
         <v>33402</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="10">
         <v>58570</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="10">
         <v>27793</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="10">
         <v>238845</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="10">
         <v>247100</v>
       </c>
-      <c r="K35" s="22">
+      <c r="K35" s="10">
         <v>-8255</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="17.5">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="22"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
@@ -5575,54 +5583,54 @@
       </c>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B125" s="22">
+      <c r="B125" s="10">
         <v>105848.66</v>
       </c>
-      <c r="C125" s="22">
+      <c r="C125" s="10">
         <v>105933.92</v>
       </c>
-      <c r="D125" s="22">
+      <c r="D125" s="10">
         <v>110577.06</v>
       </c>
-      <c r="E125" s="22">
+      <c r="E125" s="10">
         <v>108806.09</v>
       </c>
-      <c r="F125" s="22">
+      <c r="F125" s="10">
         <v>131953.81</v>
       </c>
-      <c r="G125" s="22">
+      <c r="G125" s="10">
         <v>209172.85</v>
       </c>
-      <c r="H125" s="22">
+      <c r="H125" s="10">
         <v>149555.76</v>
       </c>
-      <c r="I125" s="22">
+      <c r="I125" s="10">
         <v>921848.15</v>
       </c>
-      <c r="J125" s="22">
+      <c r="J125" s="10">
         <v>1054250</v>
       </c>
-      <c r="K125" s="22">
+      <c r="K125" s="10">
         <v>-132401.85</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="17.5">
-      <c r="A126" s="19" t="s">
+      <c r="A126" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B126" s="20"/>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
-      <c r="J126" s="20"/>
-      <c r="K126" s="21"/>
+      <c r="B126" s="21"/>
+      <c r="C126" s="21"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="21"/>
+      <c r="I126" s="21"/>
+      <c r="J126" s="21"/>
+      <c r="K126" s="22"/>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
@@ -5765,54 +5773,54 @@
       </c>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="22" t="s">
+      <c r="A131" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B131" s="22">
+      <c r="B131" s="10">
         <v>1795.63</v>
       </c>
-      <c r="C131" s="22">
+      <c r="C131" s="10">
         <v>1441</v>
       </c>
-      <c r="D131" s="22">
+      <c r="D131" s="10">
         <v>1762</v>
       </c>
-      <c r="E131" s="22">
+      <c r="E131" s="10">
         <v>1503</v>
       </c>
-      <c r="F131" s="22">
+      <c r="F131" s="10">
         <v>2067</v>
       </c>
-      <c r="G131" s="22">
+      <c r="G131" s="10">
         <v>3997</v>
       </c>
-      <c r="H131" s="22">
+      <c r="H131" s="10">
         <v>3017</v>
       </c>
-      <c r="I131" s="22">
+      <c r="I131" s="10">
         <v>15582.63</v>
       </c>
-      <c r="J131" s="22">
+      <c r="J131" s="10">
         <v>26500</v>
       </c>
-      <c r="K131" s="22">
+      <c r="K131" s="10">
         <v>-10917.37</v>
       </c>
     </row>
     <row r="132" spans="1:14" ht="17.5">
-      <c r="A132" s="19" t="s">
+      <c r="A132" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B132" s="20"/>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="20"/>
-      <c r="J132" s="20"/>
-      <c r="K132" s="21"/>
+      <c r="B132" s="21"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="21"/>
+      <c r="F132" s="21"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="21"/>
+      <c r="I132" s="21"/>
+      <c r="J132" s="21"/>
+      <c r="K132" s="22"/>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
@@ -5955,37 +5963,37 @@
       </c>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="22" t="s">
+      <c r="A137" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B137" s="22">
+      <c r="B137" s="10">
         <v>9971</v>
       </c>
-      <c r="C137" s="22">
+      <c r="C137" s="10">
         <v>11465</v>
       </c>
-      <c r="D137" s="22">
+      <c r="D137" s="10">
         <v>10625</v>
       </c>
-      <c r="E137" s="22">
+      <c r="E137" s="10">
         <v>10648</v>
       </c>
-      <c r="F137" s="22">
+      <c r="F137" s="10">
         <v>12116</v>
       </c>
-      <c r="G137" s="22">
+      <c r="G137" s="10">
         <v>15789</v>
       </c>
-      <c r="H137" s="22">
+      <c r="H137" s="10">
         <v>14693</v>
       </c>
-      <c r="I137" s="22">
+      <c r="I137" s="10">
         <v>85307</v>
       </c>
-      <c r="J137" s="22">
+      <c r="J137" s="10">
         <v>89600</v>
       </c>
-      <c r="K137" s="22">
+      <c r="K137" s="10">
         <v>-4293</v>
       </c>
       <c r="N137" t="s">
@@ -5993,19 +6001,19 @@
       </c>
     </row>
     <row r="138" spans="1:14" ht="17.5">
-      <c r="A138" s="19" t="s">
+      <c r="A138" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B138" s="20"/>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="20"/>
-      <c r="F138" s="20"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
-      <c r="I138" s="20"/>
-      <c r="J138" s="20"/>
-      <c r="K138" s="21"/>
+      <c r="B138" s="21"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="21"/>
+      <c r="J138" s="21"/>
+      <c r="K138" s="22"/>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" t="s">
@@ -6813,89 +6821,89 @@
       </c>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" t="s">
+      <c r="A162" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="23">
         <v>36950</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="23">
         <v>42011</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="23">
         <v>43862</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="23">
         <v>43115</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="23">
         <v>42816</v>
       </c>
-      <c r="G162">
+      <c r="G162" s="23">
         <v>1126</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="23">
         <v>0</v>
       </c>
-      <c r="I162">
+      <c r="I162" s="23">
         <v>209880</v>
       </c>
-      <c r="J162">
+      <c r="J162" s="23">
         <v>227800</v>
       </c>
-      <c r="K162">
+      <c r="K162" s="23">
         <v>-17920</v>
       </c>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="22" t="s">
+      <c r="A163" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="B163" s="22">
+      <c r="B163" s="24">
         <v>184009.29</v>
       </c>
-      <c r="C163" s="22">
+      <c r="C163" s="24">
         <v>191094.92</v>
       </c>
-      <c r="D163" s="22">
+      <c r="D163" s="24">
         <v>195378.06</v>
       </c>
-      <c r="E163" s="22">
+      <c r="E163" s="24">
         <v>194912.09</v>
       </c>
-      <c r="F163" s="22">
+      <c r="F163" s="24">
         <v>222354.81</v>
       </c>
-      <c r="G163" s="22">
+      <c r="G163" s="24">
         <v>288654.84999999998</v>
       </c>
-      <c r="H163" s="22">
+      <c r="H163" s="24">
         <v>195058.76</v>
       </c>
-      <c r="I163" s="22">
+      <c r="I163" s="24">
         <v>1471462.78</v>
       </c>
-      <c r="J163" s="22">
+      <c r="J163" s="24">
         <v>1645250</v>
       </c>
-      <c r="K163" s="22">
+      <c r="K163" s="24">
         <v>-173787.22</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="17.5">
-      <c r="A164" s="19" t="s">
+      <c r="A164" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B164" s="20"/>
-      <c r="C164" s="20"/>
-      <c r="D164" s="20"/>
-      <c r="E164" s="20"/>
-      <c r="F164" s="20"/>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="20"/>
-      <c r="K164" s="21"/>
+      <c r="B164" s="21"/>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
+      <c r="E164" s="21"/>
+      <c r="F164" s="21"/>
+      <c r="G164" s="21"/>
+      <c r="H164" s="21"/>
+      <c r="I164" s="21"/>
+      <c r="J164" s="21"/>
+      <c r="K164" s="22"/>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
@@ -7108,7 +7116,7 @@
       </c>
     </row>
     <row r="171" spans="1:11">
-      <c r="A171" t="s">
+      <c r="A171" s="26" t="s">
         <v>181</v>
       </c>
       <c r="B171">
@@ -7143,37 +7151,37 @@
       </c>
     </row>
     <row r="172" spans="1:11">
-      <c r="A172" s="22" t="s">
+      <c r="A172" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B172" s="22">
+      <c r="B172" s="24">
         <v>194725.47</v>
       </c>
-      <c r="C172" s="22">
+      <c r="C172" s="24">
         <v>202071.92</v>
       </c>
-      <c r="D172" s="22">
+      <c r="D172" s="24">
         <v>208117.06</v>
       </c>
-      <c r="E172" s="22">
+      <c r="E172" s="24">
         <v>207915.79</v>
       </c>
-      <c r="F172" s="22">
+      <c r="F172" s="24">
         <v>235271.31</v>
       </c>
-      <c r="G172" s="22">
+      <c r="G172" s="24">
         <v>304709.09999999998</v>
       </c>
-      <c r="H172" s="22">
+      <c r="H172" s="24">
         <v>204560.53</v>
       </c>
-      <c r="I172" s="22">
+      <c r="I172" s="24">
         <v>1557371.18</v>
       </c>
-      <c r="J172" s="22">
+      <c r="J172" s="24">
         <v>1732250</v>
       </c>
-      <c r="K172" s="22">
+      <c r="K172" s="24">
         <v>-174878.82</v>
       </c>
     </row>
@@ -7184,16 +7192,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A126:K126"/>
+    <mergeCell ref="A132:K132"/>
     <mergeCell ref="A138:K138"/>
     <mergeCell ref="A164:K164"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A126:K126"/>
-    <mergeCell ref="A132:K132"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
